--- a/pregenereated_results/s2/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/pregenereated_results/s2/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covariate_Balance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weight_Diagnostics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATE_MSM" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Propensity_Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Covariate_Balance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weight_Diagnostics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ATE_MSM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Propensity_Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,10 +483,10 @@
         <v>-0.019</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="E2" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.045</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.03</v>
+        <v>-0.014</v>
       </c>
       <c r="E4" t="n">
-        <v>0.015</v>
+        <v>-0.002</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -552,22 +552,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.097</v>
+        <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07300000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -579,22 +579,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.024</v>
+        <v>0.097</v>
       </c>
       <c r="D6" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.046</v>
+        <v>-0.024</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001</v>
+        <v>0.027</v>
       </c>
       <c r="E7" t="n">
-        <v>0.045</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.046</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.074</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.042</v>
+        <v>-0.001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.034</v>
+        <v>-0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.007</v>
+        <v>-0.042</v>
       </c>
       <c r="E10" t="n">
-        <v>0.027</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.023</v>
+        <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>0.011</v>
+        <v>-0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.012</v>
+        <v>0.026</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.007</v>
+        <v>0.023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.017</v>
+        <v>0.013</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.041</v>
+        <v>0.007</v>
       </c>
       <c r="D13" t="n">
-        <v>0.039</v>
+        <v>0.025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002000000000000002</v>
+        <v>-0.018</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.005</v>
+        <v>0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.012</v>
+        <v>0.038</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.007</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.032</v>
+        <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>0.035</v>
+        <v>-0.013</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.003000000000000003</v>
+        <v>-0.008</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.014</v>
+        <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.006</v>
+        <v>0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0</v>
+        <v>-0.014</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.003</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.008</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="E18" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.077</v>
+        <v>-0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>0.033</v>
+        <v>-0.001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.044</v>
+        <v>0.007</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.019</v>
+        <v>0.077</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.021</v>
+        <v>0.031</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.002000000000000002</v>
+        <v>0.046</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.113</v>
+        <v>-0.019</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.055</v>
+        <v>-0.023</v>
       </c>
       <c r="E21" t="n">
-        <v>0.058</v>
+        <v>-0.004</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.197</v>
+        <v>-0.113</v>
       </c>
       <c r="D22" t="n">
-        <v>0.068</v>
+        <v>-0.05</v>
       </c>
       <c r="E22" t="n">
-        <v>0.129</v>
+        <v>0.063</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.143</v>
+        <v>0.197</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.043</v>
+        <v>0.065</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.054</v>
+        <v>-0.143</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.026</v>
+        <v>-0.042</v>
       </c>
       <c r="E24" t="n">
-        <v>0.028</v>
+        <v>0.101</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.128</v>
+        <v>-0.054</v>
       </c>
       <c r="D25" t="n">
-        <v>0.016</v>
+        <v>-0.027</v>
       </c>
       <c r="E25" t="n">
-        <v>0.112</v>
+        <v>0.027</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.227</v>
+        <v>-0.128</v>
       </c>
       <c r="D26" t="n">
-        <v>0.025</v>
+        <v>0.019</v>
       </c>
       <c r="E26" t="n">
-        <v>0.202</v>
+        <v>0.109</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.392</v>
+        <v>0.227</v>
       </c>
       <c r="D27" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="E27" t="n">
-        <v>0.36</v>
+        <v>0.205</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.401</v>
+        <v>0.392</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.043</v>
+        <v>0.03</v>
       </c>
       <c r="E28" t="n">
-        <v>0.358</v>
+        <v>0.362</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.107</v>
+        <v>-0.401</v>
       </c>
       <c r="D29" t="n">
-        <v>0.044</v>
+        <v>-0.038</v>
       </c>
       <c r="E29" t="n">
-        <v>0.063</v>
+        <v>0.363</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.041</v>
+        <v>0.107</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.011</v>
+        <v>0.042</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03</v>
+        <v>0.065</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.066</v>
+        <v>-0.041</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.057</v>
+        <v>-0.013</v>
       </c>
       <c r="E31" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,27 +1281,54 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>region_Middle_East_and_Africa</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>region_North_America</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>categorical</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C33" t="n">
         <v>0.022</v>
       </c>
-      <c r="D32" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.007999999999999998</v>
-      </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" t="b">
+      <c r="D33" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1361,22 +1388,22 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7099.15044992504</v>
+        <v>7094.386718944054</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9952614504155347</v>
+        <v>0.9957648995493169</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1298633463115101</v>
+        <v>0.1325095691671194</v>
       </c>
       <c r="E2" t="n">
-        <v>1.630560047471351</v>
+        <v>1.678870188120528</v>
       </c>
       <c r="F2" t="n">
-        <v>1.129699880048327</v>
+        <v>1.124267686541995</v>
       </c>
       <c r="G2" t="n">
-        <v>1.630026169528008</v>
+        <v>1.67804342107184</v>
       </c>
     </row>
   </sheetData>
@@ -1390,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1437,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.733756418089332</v>
+        <v>1.667251009830694</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1039907371489294</v>
+        <v>0.103950564589624</v>
       </c>
       <c r="D2" t="n">
-        <v>1.529938318551659</v>
+        <v>1.463511647062426</v>
       </c>
       <c r="E2" t="n">
-        <v>1.937574517627005</v>
+        <v>1.870990372598961</v>
       </c>
       <c r="F2" t="n">
-        <v>2.086983345575478e-62</v>
+        <v>6.837236032515922e-58</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1462,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0251866492239422</v>
+        <v>-0.02463484865352594</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02065833898064545</v>
+        <v>0.02140527657651924</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06567624960642718</v>
+        <v>-0.06658841982262248</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01530295115854279</v>
+        <v>0.01731872251557061</v>
       </c>
       <c r="F3" t="n">
-        <v>0.222768249001289</v>
+        <v>0.2497826842838106</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1487,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.07590824737386069</v>
+        <v>-0.07540915009642361</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05194396280113975</v>
+        <v>0.05279509857940832</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1777165436783829</v>
+        <v>-0.1788856418723057</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02590004893066152</v>
+        <v>0.02806734167945846</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1439197457007533</v>
+        <v>0.1531951152281507</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1512,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.07780196206684177</v>
+        <v>-0.07777010843832736</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03538488674579444</v>
+        <v>0.03746669966516231</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1471550656856276</v>
+        <v>-0.1512034904016244</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.008448858448055957</v>
+        <v>-0.004336726475030334</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0278968247979421</v>
+        <v>0.03792052047519413</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1537,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02874604060112293</v>
+        <v>0.02910393820822493</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0346224613295133</v>
+        <v>0.03598696595065996</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03911273666085389</v>
+        <v>-0.0414292189679378</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09660481786309975</v>
+        <v>0.09963709538438767</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4063853354095488</v>
+        <v>0.4186672829157784</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1562,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02222604255379982</v>
+        <v>0.0238152894120912</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03458087694623684</v>
+        <v>0.03444948165300097</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.04555123081463582</v>
+        <v>-0.04370445391386407</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09000331592223547</v>
+        <v>0.09133503273804647</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5204016474802583</v>
+        <v>0.489370415995682</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1587,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03454754584913964</v>
+        <v>0.03400947065252904</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03561818328254768</v>
+        <v>0.03572753009575889</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03526281057940046</v>
+        <v>-0.03601520159172927</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1043579022776797</v>
+        <v>0.1040341428967873</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3320757683469738</v>
+        <v>0.3411415276602031</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1612,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03726879387703849</v>
+        <v>0.03806830840584246</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03507541619437008</v>
+        <v>0.03435019598273854</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.03147775860667983</v>
+        <v>-0.02925683858221754</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1060153463607568</v>
+        <v>0.1053934553939025</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2879936986170477</v>
+        <v>0.2677575867271222</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1637,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.003912324336423673</v>
+        <v>0.002048208353331531</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0564561626792934</v>
+        <v>0.05422289275560442</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1067397212203257</v>
+        <v>-0.1042267085852309</v>
       </c>
       <c r="E10" t="n">
-        <v>0.114564369893173</v>
+        <v>0.108323125291894</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9447520627399307</v>
+        <v>0.9698679804037615</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1662,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.0024821164138326</v>
+        <v>-0.002592226077109175</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05595641113994539</v>
+        <v>0.05602652915899779</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1121546669522414</v>
+        <v>-0.112402205407528</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1071904341245762</v>
+        <v>0.1072177532533097</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9646190123467583</v>
+        <v>0.9630967776380733</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1687,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.09561943247724571</v>
+        <v>-0.09685847877529365</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05438573261576761</v>
+        <v>0.05376448018771039</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2022135096769756</v>
+        <v>-0.2022349235907233</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01097464472248416</v>
+        <v>0.008517966040135994</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07871837240250922</v>
+        <v>0.07161892986848868</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1712,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05969329549461583</v>
+        <v>0.05872986129122747</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05453660979235783</v>
+        <v>0.05289827688087845</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.04719649553731995</v>
+        <v>-0.04494885623952209</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1665830865265516</v>
+        <v>0.162408578821977</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2737118276689021</v>
+        <v>0.2668949821258334</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1737,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01243413440661101</v>
+        <v>0.01177434185712835</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05489023465213786</v>
+        <v>0.05286151476865353</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09514874861453167</v>
+        <v>-0.09183232325766474</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1200170174277537</v>
+        <v>0.1153810069719214</v>
       </c>
       <c r="F14" t="n">
-        <v>0.820791360495106</v>
+        <v>0.8237383381340895</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1762,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.07985845118779195</v>
+        <v>-0.08022934381684162</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05520826813277101</v>
+        <v>0.05335891402080915</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1880646683768535</v>
+        <v>-0.1848108935517969</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02834776600126962</v>
+        <v>0.02435220591811364</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1480385790403904</v>
+        <v>0.1326897956946211</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1787,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02861026211245173</v>
+        <v>0.02854452070261685</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05373442642644981</v>
+        <v>0.0524417782095568</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07670727841330721</v>
+        <v>-0.07423947587335188</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1339278026382107</v>
+        <v>0.1313285172785856</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5944225231123578</v>
+        <v>0.5862290010152384</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1812,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0107837610566011</v>
+        <v>0.009535077288637601</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05471602927687293</v>
+        <v>0.05256744027004785</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09645768570310903</v>
+        <v>-0.09349521240011668</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1180252078163112</v>
+        <v>0.1125653669773919</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8437602716876919</v>
+        <v>0.8560634189937375</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1837,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09245858798322955</v>
+        <v>-0.09439860867570241</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05640131288875536</v>
+        <v>0.05484958712397588</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2030031299259648</v>
+        <v>-0.201901824005587</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01808595395950571</v>
+        <v>0.0131046066541822</v>
       </c>
       <c r="F18" t="n">
-        <v>0.101151106933479</v>
+        <v>0.08524265511921764</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1862,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03313744987870552</v>
+        <v>-0.03376783026243109</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0544090489154346</v>
+        <v>0.05194237008077477</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1397772261860354</v>
+        <v>-0.1355730048924005</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07350232642862438</v>
+        <v>0.06803734436753832</v>
       </c>
       <c r="F19" t="n">
-        <v>0.542495943531903</v>
+        <v>0.5156264420353127</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1887,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.02607572656962338</v>
+        <v>-0.02764259828225421</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05488235741562991</v>
+        <v>0.05243646023149125</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1336431704909128</v>
+        <v>-0.1304161718127439</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08149171735166601</v>
+        <v>0.07513097524823546</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6347011723484537</v>
+        <v>0.5980799157062464</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1912,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05229675757103883</v>
+        <v>-0.05277599238898848</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0531381845608908</v>
+        <v>0.05170157742489209</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1564456855142271</v>
+        <v>-0.1541092220856861</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05185217037214947</v>
+        <v>0.04855723730770913</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3250342421248235</v>
+        <v>0.3073581670729142</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1937,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03787644393963902</v>
+        <v>-0.03816573212201307</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05433640727107439</v>
+        <v>0.05200730262192996</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1443738452402452</v>
+        <v>-0.1400981721940713</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0686209573609671</v>
+        <v>0.06376670795004519</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4857570928288926</v>
+        <v>0.4630381345915038</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1962,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.05972689773741191</v>
+        <v>-0.05938706149335551</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05554007552661697</v>
+        <v>0.05429573538926734</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1685834454682156</v>
+        <v>-0.1658047473704364</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04912964999339182</v>
+        <v>0.04703062438372533</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2822029295577292</v>
+        <v>0.2740557435063636</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -1987,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.00961508332570052</v>
+        <v>0.008451758672660589</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04676583923458347</v>
+        <v>0.04715478622950783</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.08204427728087328</v>
+        <v>-0.08396992403586005</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1012744439322743</v>
+        <v>0.1008734413811812</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8371029301957951</v>
+        <v>0.857753672816564</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2012,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.008830828840539475</v>
+        <v>0.008266388421399361</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02649064084286979</v>
+        <v>0.02616363601935622</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04308987313887109</v>
+        <v>-0.04301339588115373</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06075153081995004</v>
+        <v>0.05954617272395245</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7388651515184921</v>
+        <v>0.7520408188561629</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2037,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02432357632612914</v>
+        <v>0.02423811373715813</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03175489478123929</v>
+        <v>0.03264857083897</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0379148737779588</v>
+        <v>-0.03975190925392773</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08656202643021707</v>
+        <v>0.08822813672824399</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4436889142082463</v>
+        <v>0.4578484564206015</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2062,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03988149110508888</v>
+        <v>-0.0391593403491267</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03242425669874236</v>
+        <v>0.03173000514229339</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1034318664601055</v>
+        <v>-0.1013490076572925</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02366888424992774</v>
+        <v>0.02303032695903906</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2187010850925784</v>
+        <v>0.2171498974623944</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2087,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.01809571296940621</v>
+        <v>0.0192295424242075</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03176084688260914</v>
+        <v>0.03227805668499568</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.04415440303899895</v>
+        <v>-0.04403428616932635</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08034582897781138</v>
+        <v>0.08249337101774136</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5688479032840155</v>
+        <v>0.5513445242495112</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2112,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0665527026447531</v>
+        <v>0.06730170037260196</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03224234159839069</v>
+        <v>0.03196767543970733</v>
       </c>
       <c r="D29" t="n">
-        <v>0.003358874334669748</v>
+        <v>0.004646207841309952</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1297465309548365</v>
+        <v>0.129957192903894</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03900445712679831</v>
+        <v>0.035264785038513</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2137,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0408092366185924</v>
+        <v>-0.04059280522771685</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04202937973037035</v>
+        <v>0.04219295914182773</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.123185307182676</v>
+        <v>-0.1232894855468692</v>
       </c>
       <c r="E30" t="n">
-        <v>0.04156683394549125</v>
+        <v>0.04210387509143552</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3315635759904207</v>
+        <v>0.3360117637295977</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2158,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.003672284887981821</v>
+        <v>-0.0009948915328936545</v>
       </c>
       <c r="C31" t="n">
-        <v>0.004355603727972489</v>
+        <v>0.001577711740423721</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0122091113257363</v>
+        <v>-0.004087149722110155</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004864541549772653</v>
+        <v>0.002097366656322845</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3991628399685549</v>
+        <v>0.5283076912307983</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2187,19 +2214,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.003356307374552061</v>
+        <v>0.003364288003062576</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001760036731275895</v>
+        <v>0.001764656162787906</v>
       </c>
       <c r="D32" t="n">
-        <v>-9.330123021629531e-05</v>
+        <v>-9.437452109837185e-05</v>
       </c>
       <c r="E32" t="n">
-        <v>0.006805915979320416</v>
+        <v>0.006822950527223523</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05652667035326574</v>
+        <v>0.05658749372658557</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2208,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0009853319469101778</v>
+        <v>3.375687514584261e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001523788313352139</v>
+        <v>0.004788621486128006</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003971902161143405</v>
+        <v>-0.009351768773259718</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00200123826732305</v>
+        <v>0.009419282523551403</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5178694362050331</v>
+        <v>0.9943754446863979</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2233,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.02744176820215817</v>
+        <v>0.4490526515310966</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02417734703750178</v>
+        <v>0.01068393144388248</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.07482849763738783</v>
+        <v>0.428112530687792</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01994496123307149</v>
+        <v>0.4699927723744013</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2563670119804993</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2258,25 +2285,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4488274554177198</v>
+        <v>-0.02814404589903955</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01063177204819388</v>
+        <v>0.02420739120983631</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4279895651114202</v>
+        <v>-0.0755896608299902</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4696653457240194</v>
+        <v>0.01930156903191111</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.2449828954760783</v>
       </c>
       <c r="G35" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>tot_span_of_control</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.001861597274177133</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.001577846052651465</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.001230924162168428</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.004954118710522693</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.2380660284989626</v>
+      </c>
+      <c r="G36" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2291,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2323,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.424595366175215</v>
+        <v>-2.680600179802938</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4699812973694731</v>
+        <v>0.4771933030981325</v>
       </c>
       <c r="D2" t="n">
-        <v>2.483799515165129e-07</v>
+        <v>1.938181768271168e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2339,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02313926327040559</v>
+        <v>-0.02542074333516161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09767081015513708</v>
+        <v>0.1002143663033997</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8127260429188259</v>
+        <v>0.79975540801217</v>
       </c>
     </row>
     <row r="4">
@@ -2355,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2234052412627192</v>
+        <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2328794775545217</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3373990748904945</v>
+        <v>0.3364439424069159</v>
       </c>
     </row>
     <row r="5">
@@ -2371,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8180627404127299</v>
+        <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1689953683152051</v>
+        <v>0.1734026513921177</v>
       </c>
       <c r="D5" t="n">
-        <v>1.293561359606461e-06</v>
+        <v>2.563995828054277e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2387,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03544498749496686</v>
+        <v>0.03527526670387295</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1931765738941879</v>
+        <v>0.191688294691954</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8544175529024153</v>
+        <v>0.853994545471355</v>
       </c>
     </row>
     <row r="7">
@@ -2403,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.275906022416754</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1812662634417183</v>
+        <v>0.1901447102133382</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1279831375553563</v>
+        <v>0.1446466431125516</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1078851505724593</v>
+        <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1932040242209362</v>
+        <v>0.1952515666982443</v>
       </c>
       <c r="D8" t="n">
-        <v>0.576571189971413</v>
+        <v>0.5954095400432464</v>
       </c>
     </row>
     <row r="9">
@@ -2435,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.871778570870576</v>
+        <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1678649218702299</v>
+        <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>2.065613561488396e-07</v>
+        <v>2.539495077342701e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2451,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.037352240367789</v>
+        <v>-0.04456520772617086</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2698916813503851</v>
+        <v>0.2604021031716313</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8899265467947022</v>
+        <v>0.8641137091517834</v>
       </c>
     </row>
     <row r="11">
@@ -2467,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2713985237416621</v>
+        <v>-0.2737623724798149</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2816070653033665</v>
+        <v>0.2787881385465057</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3351717882228968</v>
+        <v>0.3261132423877617</v>
       </c>
     </row>
     <row r="12">
@@ -2483,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08472740319905862</v>
+        <v>0.08100487957118127</v>
       </c>
       <c r="C12" t="n">
-        <v>0.258092362680186</v>
+        <v>0.2596429772097166</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7426974971355069</v>
+        <v>0.7550514391424692</v>
       </c>
     </row>
     <row r="13">
@@ -2499,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04068301518422479</v>
+        <v>0.03917827337461736</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2611004784975071</v>
+        <v>0.2572958805743769</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8761799211234182</v>
+        <v>0.8789745077123745</v>
       </c>
     </row>
     <row r="14">
@@ -2515,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05345693884495933</v>
+        <v>-0.05296103812307947</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2638638610262009</v>
+        <v>0.2610089865588713</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8394532575785491</v>
+        <v>0.8392062624375523</v>
       </c>
     </row>
     <row r="15">
@@ -2531,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1239335042277773</v>
+        <v>0.1181322726534159</v>
       </c>
       <c r="C15" t="n">
-        <v>0.25992806241409</v>
+        <v>0.2572294350577177</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6335050825508384</v>
+        <v>0.646055612898408</v>
       </c>
     </row>
     <row r="16">
@@ -2547,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.001862882312141687</v>
+        <v>-0.004000986240379581</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2575901907586843</v>
+        <v>0.2383903410311186</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9942297799667277</v>
+        <v>0.9866094604655129</v>
       </c>
     </row>
     <row r="17">
@@ -2563,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1116424378426662</v>
+        <v>0.1057185310395304</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2586555011338381</v>
+        <v>0.2543340222421748</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6660132626676296</v>
+        <v>0.6776529122567303</v>
       </c>
     </row>
     <row r="18">
@@ -2579,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1317171712348868</v>
+        <v>-0.1377694895733256</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2668604874679544</v>
+        <v>0.2636874203313626</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6216023734866079</v>
+        <v>0.6013412201546261</v>
       </c>
     </row>
     <row r="19">
@@ -2595,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02274331928780688</v>
+        <v>-0.02557154094223238</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2635260713514327</v>
+        <v>0.252759790153811</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9312248636975232</v>
+        <v>0.9194160355966675</v>
       </c>
     </row>
     <row r="20">
@@ -2611,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06665392434463961</v>
+        <v>-0.07344622569376427</v>
       </c>
       <c r="C20" t="n">
-        <v>0.265659520794061</v>
+        <v>0.267457860954101</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8018915682492664</v>
+        <v>0.7836169672222772</v>
       </c>
     </row>
     <row r="21">
@@ -2627,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2096018965396373</v>
+        <v>0.2063167170305059</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2485899459155399</v>
+        <v>0.244289653245072</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3991371714945826</v>
+        <v>0.3983578134719846</v>
       </c>
     </row>
     <row r="22">
@@ -2643,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1668969509214496</v>
+        <v>-0.1704634573362026</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2747515009079846</v>
+        <v>0.2696748454965904</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5435543635085022</v>
+        <v>0.5273167196806361</v>
       </c>
     </row>
     <row r="23">
@@ -2659,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4971940641810814</v>
+        <v>-0.5008110927334757</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2924423511374601</v>
+        <v>0.287067218044571</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08910387128184533</v>
+        <v>0.08105838975171785</v>
       </c>
     </row>
     <row r="24">
@@ -2675,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.939948370751521</v>
+        <v>0.9366864721074267</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1570978378415049</v>
+        <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.187908098302239e-09</v>
+        <v>2.713396260923891e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2691,13 +2743,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5774584503453005</v>
+        <v>-0.5776106069409677</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1153148485868671</v>
+        <v>0.1143619392421807</v>
       </c>
       <c r="D25" t="n">
-        <v>5.50935246170832e-07</v>
+        <v>4.401383208103943e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2707,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2375989005820144</v>
+        <v>0.237316144844174</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1483942012834082</v>
+        <v>0.1503781926377478</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1093473930483596</v>
+        <v>0.1145360411757813</v>
       </c>
     </row>
     <row r="27">
@@ -2723,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04390400011939626</v>
+        <v>-0.04350476117998651</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1581709974635947</v>
+        <v>0.1611879340386412</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7813401518906566</v>
+        <v>0.7872365295400213</v>
       </c>
     </row>
     <row r="28">
@@ -2739,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07706864556787009</v>
+        <v>-0.07514354096975732</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1578050341313147</v>
+        <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6252814998540484</v>
+        <v>0.6414556246120151</v>
       </c>
     </row>
     <row r="29">
@@ -2755,29 +2807,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09735884295377209</v>
+        <v>0.09749293462742097</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1528329758433737</v>
+        <v>0.1543265796290165</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5241067842939673</v>
+        <v>0.5275624553510008</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0214099884697233</v>
+        <v>-0.002418133412192873</v>
       </c>
       <c r="C30" t="n">
-        <v>0.02125751820946937</v>
+        <v>0.007135781003458546</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3138518697701007</v>
+        <v>0.7347043603418277</v>
       </c>
     </row>
     <row r="31">
@@ -2787,29 +2839,29 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.004963851467081969</v>
+        <v>-0.005012017390962195</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008295015527615652</v>
+        <v>0.008304876992455039</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5495638837811058</v>
+        <v>0.5461741835341576</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.002369150025834419</v>
+        <v>-0.004129656026475419</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007250684388774151</v>
+        <v>0.02222260881033174</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7438581373219401</v>
+        <v>0.8525770672961279</v>
       </c>
     </row>
     <row r="33">
@@ -2819,13 +2871,29 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.228992117455078</v>
+        <v>0.2280638724458785</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1106079911201261</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D33" t="n">
-        <v>0.03842392670187963</v>
+        <v>0.04668969945129923</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>tot_span_of_control</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.006335499136474495</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.006871422968197181</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.3565249957666435</v>
       </c>
     </row>
   </sheetData>
